--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI13"/>
+  <dimension ref="A1:CI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,42 +878,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,275 +1014,275 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>13901569.95086705</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-149855.61</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>16.42</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>13908427.44790159</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-379221.83</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>11.16750432561588</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-0.1554013053709651</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-2.991995416491073</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>6.27</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>9.47</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>59.51%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>8.78%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1309,104 +1309,104 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,32 +1455,32 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-379289.53</v>
+        <v>-379221.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,37 +1643,37 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1740,104 +1740,104 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,275 +1876,275 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>13901569.95086705</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-379289.53</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>16.42</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>60.6</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>13908427.44790159</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-292541.83</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>11.16750432561588</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-0.1554013053709651</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-2.991995416491073</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>6.27</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>9.47</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>59.51%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>8.78%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.488</t>
+          <t>68.327</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-25.16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,42 +2317,42 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-336102.7</v>
+        <v>-292541.83</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2505,37 +2505,37 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2602,42 +2602,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>41.488</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>46.504</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>93.16</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.05999999999999</t>
+          <t>60.26000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.88</t>
+          <t>-118.23</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2843651.0</t>
+          <t>2526671.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>5017353.6</t>
+          <t>4511370.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4610095.3</t>
+          <t>4642479.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>5974136.06</t>
+          <t>5957114.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>407258</t>
+          <t>-131109</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-227808.4429917456</t>
+          <t>-244469.0978557485</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-211959.74</v>
+        <v>-336102.7</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,27 +2906,27 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,37 +2936,37 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,27 +2986,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>83.932</t>
+          <t>46.504</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,64 +3179,64 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>60.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>60.76</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>60.13</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>59.92</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>60.58</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>60.71</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-38.95</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.16</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-118.88</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5086341.0</t>
+          <t>2843651.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>5219933.4</t>
+          <t>5017353.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4784238.5</t>
+          <t>4610095.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>5969370.9</t>
+          <t>5974136.06</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>435694</t>
+          <t>407258</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-230690.0258833168</t>
+          <t>-227808.4429917456</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-61004.8</v>
+        <v>-211959.74</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3367,37 +3367,37 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.985</t>
+          <t>83.932</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,72 +3600,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-100.50</t>
+          <t>-38.95</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.89</t>
+          <t>-118.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2378380.0</t>
+          <t>5086341.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5295714.0</t>
+          <t>5219933.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4540247.8</t>
+          <t>4784238.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>5965162.52</t>
+          <t>5969370.9</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>755466</t>
+          <t>435694</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-261541.8851309825</t>
+          <t>-230690.0258833168</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-83464.36</v>
+        <v>-61004.8</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,67 +3768,67 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>164.393</t>
+          <t>39.985</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,52 +4031,52 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>59.84</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-100.50</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.65</t>
+          <t>-116.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9721808.0</t>
+          <t>2378380.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5681831.6</t>
+          <t>5295714.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4455830.2</t>
+          <t>4540247.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>6056392.34</t>
+          <t>5965162.52</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1226001</t>
+          <t>755466</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-293919.6167269187</t>
+          <t>-261541.8851309825</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>177570.1</v>
+        <v>-83464.36</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,67 +4199,67 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,27 +4279,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>84.128</t>
+          <t>164.393</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,42 +4472,42 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.55999999999999</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.64</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-141.63</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.48</t>
+          <t>-112.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5056588.0</t>
+          <t>9721808.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4773588.6</t>
+          <t>5681831.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3734529.4</t>
+          <t>4455830.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>5904347.04</t>
+          <t>6056392.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1039059</t>
+          <t>1226001</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-379645.0197043647</t>
+          <t>-293919.6167269187</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-242661.17</v>
+        <v>177570.1</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,17 +4630,17 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
@@ -4655,42 +4655,42 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,27 +4710,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>63.783</t>
+          <t>84.128</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,52 +4893,52 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.64</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>60.55999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>61.18</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.64</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-174.76</t>
+          <t>-141.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.48</t>
+          <t>-108.48</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3856550.0</t>
+          <t>5056588.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4202837.0</t>
+          <t>4773588.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3751134.0</t>
+          <t>3734529.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>5935671.66</t>
+          <t>5904347.04</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>451703</t>
+          <t>1039059</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-404551.1734857985</t>
+          <t>-379645.0197043647</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-334480.09</v>
+        <v>-242661.17</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
@@ -5086,42 +5086,42 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,27 +5141,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>63.783</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21.07</t>
+          <t>14.97</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>53.64</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.64000000000001</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>61.32</t>
+          <t>61.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.57</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>60.06</t>
+          <t>60.07</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-298.43</t>
+          <t>-174.76</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.08</t>
+          <t>-105.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13908427.44790159</t>
+          <t>13901569.95086705</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5465244.0</t>
+          <t>3856550.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4348543.6</t>
+          <t>4202837.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4666754.1</t>
+          <t>3751134.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>5955044.5</t>
+          <t>5935671.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-318210</t>
+          <t>451703</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-417291.3697189604</t>
+          <t>-404551.1734857985</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-325128.76</v>
+        <v>-334480.09</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>11.16750432561588</t>
+          <t>6.623031455188929</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-0.1554013053709651</t>
+          <t>3.641068997764138</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-2.991995416491073</t>
+          <t>-2.243137714835828</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,37 +5522,37 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>59.51%</t>
+          <t>58.62%</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>8.78%</t>
+          <t>11.94%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,27 +5572,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>39.24</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>263.992</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.06</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,288 +5750,4598 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>55.12</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>56.86</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>59.28</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-28.39</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-113.48</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>29982893.4</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>27325142.8</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>70871687.6</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>2657750</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-4799229.377777515</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>-2145262.02</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>54.6</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>859.439</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-3.95</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>55.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>57.07</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>59.42</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-20.32</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-112.52</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>30810714.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>28427276.6</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>71965384.46</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>2383438</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-5281768.897985027</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>-1598621.31</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>952.128</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-10.08</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>56.22000000000001</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>57.31</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>59.56</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>59.23</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-8.99</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-111.89</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>25992585.6</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>25254632.5</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>72823093.42</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>737953</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-5951432.094936458</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>-3313920.55</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>-5.31</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>281.766</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-6.19</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-9.90</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-7.97</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-3.61</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>56.66</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>57.52</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>59.68</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-111.62</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>20762488.6</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>23044675.4</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>73396602.94</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-2282186</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-6430979.648412267</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>-6293886.05</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>-3.08</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>196.879</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-5.82</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-13.59</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-8.29</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-3.72</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>56.88</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>57.57</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>59.79</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-111.56</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>11143003.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>21951634.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>25405032.7</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>75419606.76</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-3453398</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-6455905.757767605</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>-6375046.04</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>485.041</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-5.63</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-9.51</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-8.46</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>23.08</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>57.72</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>59.92</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>59.23</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-4.50</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-111.42</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>27154672.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>24667392.2</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>27258318.2</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>79188309.68</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-2590926</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-6470607.524677305</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>-5741199.81</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>401.833</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-6.02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-8.13</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>49.27</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>57.38</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>57.97</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>60.04</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>59.22</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-111.30</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>22755797.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>26043838.6</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>27711987.6</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>85688285.96</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-1668149</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-6603227.108476495</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-6346198.32</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>464.395</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-7.88</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-32.37</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-6.50</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>69.23</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>58.24</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>57.54</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-111.26</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>26742952.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>24516679.4</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>36252527.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>89433496.94</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-11735848</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-6649959.615648801</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-6512523.92</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>382.341</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-37.15</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-6.18</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>78.57</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>51.83</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>58.42</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-111.36</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>21961747.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>25326862.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>40297305.9</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>89685508.6</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-14970443</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-6674947.923535203</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-6944736.97</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>56.1</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>429.27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-30.09</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-6.83</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>26.92</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>8.97</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>57.12</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>58.88</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.19</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>59.19</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-24.21</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>34.62</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-2.69</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>57.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>58.55</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>59.18</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-7.33</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-110.81</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>340708181.0159091</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>15120001.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>29380136.6</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>42619865.8</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>90864066.74</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-13239729</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-6583586.088250012</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-7195021.75</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-111.35</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>24721793.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>28858431.2</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>41279456.2</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>89986915.22</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-12421025</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-6625895.370469017</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-6801885.89</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>-1.88</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BH22" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BI22" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>1.421423718361266</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>9.706318657345912</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>7.884764051476033</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BR22" t="inlineStr">
         <is>
           <t>2.69</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CA22" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CH22" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>585.383</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-8.63</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-29.49</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-5.85</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>25.64</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>57.16</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-11.72</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-111.14</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>34036904.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>29849244.2</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>42331695.0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>90805826.98</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-12482450</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-6593897.095029591</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-6650607.63</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,57 +1009,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>60.98</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3692078.8</t>
+          <t>4057381.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>5967041.12</t>
+          <t>6008820.04</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-149855.61</v>
+        <v>-117216.2</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,42 +1309,42 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,275 +1440,275 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>13890932.43722944</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-149855.61</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>6.27</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>16.33</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>7240</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>13901569.95086705</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-379221.83</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,104 +1740,104 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,32 +1886,32 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-379289.53</v>
+        <v>-379221.83</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2171,89 +2171,89 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,275 +2302,275 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>13890932.43722944</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-379289.53</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>6.27</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>16.33</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>7240</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>13901569.95086705</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-292541.83</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,89 +2602,89 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>68.327</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>41.488</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-25.16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-2.82</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,42 +2748,42 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-336102.7</v>
+        <v>-292541.83</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,127 +3033,127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>41.488</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>46.504</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>9.74</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>-0.16</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>8.83</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10.92</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>93.16</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.05999999999999</t>
+          <t>60.26000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.88</t>
+          <t>-118.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2843651.0</t>
+          <t>2526671.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>5017353.6</t>
+          <t>4511370.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4610095.3</t>
+          <t>4642479.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>5974136.06</t>
+          <t>5957114.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>407258</t>
+          <t>-131109</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-227808.4429917456</t>
+          <t>-244469.0978557485</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-211959.74</v>
+        <v>-336102.7</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>83.932</t>
+          <t>46.504</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,64 +3610,64 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>60.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>60.76</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>60.13</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>59.92</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>60.58</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>60.71</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-38.95</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.16</t>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-118.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5086341.0</t>
+          <t>2843651.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5219933.4</t>
+          <t>5017353.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4784238.5</t>
+          <t>4610095.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>5969370.9</t>
+          <t>5974136.06</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>435694</t>
+          <t>407258</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-230690.0258833168</t>
+          <t>-227808.4429917456</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-61004.8</v>
+        <v>-211959.74</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>39.985</t>
+          <t>83.932</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-100.50</t>
+          <t>-38.95</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.89</t>
+          <t>-118.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2378380.0</t>
+          <t>5086341.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5295714.0</t>
+          <t>5219933.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4540247.8</t>
+          <t>4784238.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5965162.52</t>
+          <t>5969370.9</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>755466</t>
+          <t>435694</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-261541.8851309825</t>
+          <t>-230690.0258833168</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-83464.36</v>
+        <v>-61004.8</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>164.393</t>
+          <t>39.985</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,57 +4457,57 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>59.84</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-100.50</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.65</t>
+          <t>-116.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9721808.0</t>
+          <t>2378380.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5681831.6</t>
+          <t>5295714.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4455830.2</t>
+          <t>4540247.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>6056392.34</t>
+          <t>5965162.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1226001</t>
+          <t>755466</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-293919.6167269187</t>
+          <t>-261541.8851309825</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>177570.1</v>
+        <v>-83464.36</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>84.128</t>
+          <t>164.393</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,42 +4903,42 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.55999999999999</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.64</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-141.63</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.48</t>
+          <t>-112.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5056588.0</t>
+          <t>9721808.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4773588.6</t>
+          <t>5681831.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>3734529.4</t>
+          <t>4455830.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>5904347.04</t>
+          <t>6056392.34</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1039059</t>
+          <t>1226001</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-379645.0197043647</t>
+          <t>-293919.6167269187</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-242661.17</v>
+        <v>177570.1</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>63.783</t>
+          <t>84.128</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,57 +5319,57 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.64</t>
+          <t>23.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>60.55999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>61.18</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.64</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-174.76</t>
+          <t>-141.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.48</t>
+          <t>-108.48</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13901569.95086705</t>
+          <t>13890932.43722944</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3856550.0</t>
+          <t>5056588.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4202837.0</t>
+          <t>4773588.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3751134.0</t>
+          <t>3734529.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>5935671.66</t>
+          <t>5904347.04</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>451703</t>
+          <t>1039059</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-404551.1734857985</t>
+          <t>-379645.0197043647</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-334480.09</v>
+        <v>-242661.17</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,42 +6196,42 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,17 +7043,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7063,59 +7063,59 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,57 +7474,57 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7732,17 +7732,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,64 +8351,64 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,72 +8767,72 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-10.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>429.27</t>
+          <t>382.341</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-37.15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,52 +9629,52 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.17999999999999</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>58.55</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,17 +9684,17 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-111.36</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>24721793.0</t>
+          <t>21961747.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>28858431.2</t>
+          <t>25326862.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41279456.2</t>
+          <t>40297305.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>89986915.22</t>
+          <t>89685508.6</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-12421025</t>
+          <t>-14970443</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6625895.370469017</t>
+          <t>-6674947.923535203</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6801885.89</v>
+        <v>-6944736.97</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>585.383</t>
+          <t>429.27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-10.4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>57.17999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.55</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.18</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.14</t>
+          <t>-111.35</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>34036904.0</t>
+          <t>24721793.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>29849244.2</t>
+          <t>28858431.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>42331695.0</t>
+          <t>41279456.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>90805826.98</t>
+          <t>89986915.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-12482450</t>
+          <t>-12421025</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6593897.095029591</t>
+          <t>-6625895.370469017</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6650607.63</v>
+        <v>-6801885.89</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,260 +1024,260 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>60.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>60.5</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>60.18</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>61.05</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-110.23</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>13884806.94596542</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>6426561.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>4511870.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>3954850.9</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>6073354.68</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>557019</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-196415.2041115164</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>64065.22</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>16.42</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>22.49</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>60.98</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>60.17</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-111.80</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>13890932.43722944</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>4353182.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4057381.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>4284375.6</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6008820.04</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-226994</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-243775.2808147359</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-117216.2</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>6.27</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>60.98</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>3692078.8</t>
+          <t>4057381.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>5967041.12</t>
+          <t>6008820.04</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-149855.61</v>
+        <v>-117216.2</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,42 +1740,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,275 +1871,275 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>13884806.94596542</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-149855.61</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>16.42</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>22.49</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>13890932.43722944</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-379221.83</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>6.27</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,104 +2171,104 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,32 +2317,32 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-379289.53</v>
+        <v>-379221.83</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,17 +2555,17 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2602,104 +2602,104 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,275 +2733,275 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>13884806.94596542</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>-379289.53</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>16.42</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>22.49</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>13890932.43722944</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-292541.83</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>6.27</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>7240</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.488</t>
+          <t>68.327</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-25.16</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,42 +3179,42 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-336102.7</v>
+        <v>-292541.83</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3464,42 +3464,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>41.488</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>46.504</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>93.16</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.05999999999999</t>
+          <t>60.26000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.88</t>
+          <t>-118.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2843651.0</t>
+          <t>2526671.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>5017353.6</t>
+          <t>4511370.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4610095.3</t>
+          <t>4642479.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>5974136.06</t>
+          <t>5957114.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>407258</t>
+          <t>-131109</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-227808.4429917456</t>
+          <t>-244469.0978557485</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-211959.74</v>
+        <v>-336102.7</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>83.932</t>
+          <t>46.504</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,64 +4041,64 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>60.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>60.76</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>60.13</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>59.92</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>60.58</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>60.71</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-38.95</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.16</t>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-118.88</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5086341.0</t>
+          <t>2843651.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5219933.4</t>
+          <t>5017353.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4784238.5</t>
+          <t>4610095.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5969370.9</t>
+          <t>5974136.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>435694</t>
+          <t>407258</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-230690.0258833168</t>
+          <t>-227808.4429917456</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-61004.8</v>
+        <v>-211959.74</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>39.985</t>
+          <t>83.932</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-100.50</t>
+          <t>-38.95</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.89</t>
+          <t>-118.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2378380.0</t>
+          <t>5086341.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5295714.0</t>
+          <t>5219933.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4540247.8</t>
+          <t>4784238.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>5965162.52</t>
+          <t>5969370.9</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>755466</t>
+          <t>435694</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-261541.8851309825</t>
+          <t>-230690.0258833168</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-83464.36</v>
+        <v>-61004.8</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>164.393</t>
+          <t>39.985</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,57 +4888,57 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>59.84</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-100.50</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.65</t>
+          <t>-116.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>9721808.0</t>
+          <t>2378380.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5681831.6</t>
+          <t>5295714.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4455830.2</t>
+          <t>4540247.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>6056392.34</t>
+          <t>5965162.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1226001</t>
+          <t>755466</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-293919.6167269187</t>
+          <t>-261541.8851309825</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>177570.1</v>
+        <v>-83464.36</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>84.128</t>
+          <t>164.393</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,42 +5334,42 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>23.33</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.55999999999999</t>
+          <t>60.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.82</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.64</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-141.63</t>
+          <t>-131.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.48</t>
+          <t>-112.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13890932.43722944</t>
+          <t>13884806.94596542</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5056588.0</t>
+          <t>9721808.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4773588.6</t>
+          <t>5681831.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3734529.4</t>
+          <t>4455830.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>5904347.04</t>
+          <t>6056392.34</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1039059</t>
+          <t>1226001</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-379645.0197043647</t>
+          <t>-293919.6167269187</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-242661.17</v>
+        <v>177570.1</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7240</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>60.2</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>59.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1044878.26</v>
+        <v>-1885548.44</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,42 +6627,42 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,17 +7474,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7494,59 +7494,59 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,57 +7905,57 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8163,17 +8163,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,64 +8782,64 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.79</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,72 +9198,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>429.27</t>
+          <t>382.341</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.4</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-37.15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.17999999999999</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>58.55</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-111.36</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>24721793.0</t>
+          <t>21961747.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>28858431.2</t>
+          <t>25326862.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41279456.2</t>
+          <t>40297305.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>89986915.22</t>
+          <t>89685508.6</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-12421025</t>
+          <t>-14970443</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6625895.370469017</t>
+          <t>-6674947.923535203</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6801885.89</v>
+        <v>-6944736.97</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4511870.0</t>
+          <t>4989374.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>6073354.68</t>
+          <t>6088981.8</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>64065.22</v>
+        <v>73437.36</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1267,17 +1267,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,260 +1455,260 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>60.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>60.5</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>60.18</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>61.05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-110.23</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>13875363.1618705</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>6426561.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>4511870.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>3954850.9</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>6073354.68</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>557019</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-196415.2041115164</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>64065.22</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>16.66</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>60.98</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>60.17</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-111.80</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>13884806.94596542</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>4353182.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4057381.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>4284375.6</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>6008820.04</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-226994</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-243775.2808147359</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-117216.2</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1871,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>60.98</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3692078.8</t>
+          <t>4057381.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>5967041.12</t>
+          <t>6008820.04</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-149855.61</v>
+        <v>-117216.2</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,42 +2171,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,275 +2302,275 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>13875363.1618705</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>-149855.61</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>16.66</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>13884806.94596542</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-379221.83</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,104 +2602,104 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,32 +2748,32 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-379289.53</v>
+        <v>-379221.83</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3033,89 +3033,89 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,275 +3164,275 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>13875363.1618705</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>-379289.53</v>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>6.15</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>16.66</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>7383</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>13884806.94596542</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-292541.83</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>16.42</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.488</t>
+          <t>68.327</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-25.16</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,42 +3610,42 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-336102.7</v>
+        <v>-292541.83</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3895,127 +3895,127 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>41.488</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>46.504</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-2.56</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>9.74</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>-0.16</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>8.83</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10.92</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>93.16</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.05999999999999</t>
+          <t>60.26000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-118.88</t>
+          <t>-118.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2843651.0</t>
+          <t>2526671.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>5017353.6</t>
+          <t>4511370.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4610095.3</t>
+          <t>4642479.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5974136.06</t>
+          <t>5957114.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>407258</t>
+          <t>-131109</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-227808.4429917456</t>
+          <t>-244469.0978557485</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-211959.74</v>
+        <v>-336102.7</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>83.932</t>
+          <t>46.504</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,64 +4472,64 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>60.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>60.76</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>60.13</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>59.92</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>60.58</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>60.71</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-38.95</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.16</t>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-118.88</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5086341.0</t>
+          <t>2843651.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5219933.4</t>
+          <t>5017353.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4784238.5</t>
+          <t>4610095.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>5969370.9</t>
+          <t>5974136.06</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>435694</t>
+          <t>407258</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-230690.0258833168</t>
+          <t>-227808.4429917456</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-61004.8</v>
+        <v>-211959.74</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4645,12 +4645,12 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>39.985</t>
+          <t>83.932</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16.64</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>59.84</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.58</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.71</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-100.50</t>
+          <t>-38.95</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.89</t>
+          <t>-118.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2378380.0</t>
+          <t>5086341.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5295714.0</t>
+          <t>5219933.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4540247.8</t>
+          <t>4784238.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>5965162.52</t>
+          <t>5969370.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>755466</t>
+          <t>435694</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-261541.8851309825</t>
+          <t>-230690.0258833168</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-83464.36</v>
+        <v>-61004.8</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>164.393</t>
+          <t>39.985</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>16.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,57 +5319,57 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.16</t>
+          <t>59.84</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>60.82</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5379,17 +5379,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-131.94</t>
+          <t>-100.50</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.65</t>
+          <t>-116.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13884806.94596542</t>
+          <t>13875363.1618705</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9721808.0</t>
+          <t>2378380.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5681831.6</t>
+          <t>5295714.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4455830.2</t>
+          <t>4540247.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>6056392.34</t>
+          <t>5965162.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1226001</t>
+          <t>755466</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-293919.6167269187</t>
+          <t>-261541.8851309825</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>177570.1</v>
+        <v>-83464.36</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.66</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7383</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.8</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,72 +5755,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1885548.44</v>
+        <v>-3089720.84</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-1044878.26</v>
+        <v>-1885548.44</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,42 +7058,42 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7925,59 +7925,59 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,52 +8341,52 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,72 +8772,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,64 +9213,64 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,67 +9634,67 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,72 +10065,72 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.21</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4995542.0</t>
+          <t>4182707.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>6064700.48</t>
+          <t>6008274.14</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3208356</v>
+        <v>2044522</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,32 +1450,32 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1485,42 +1485,42 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4989374.0</t>
+          <t>4995542.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>6088981.8</t>
+          <t>6064700.48</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>4880918</v>
+        <v>3208356</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,50 +1976,50 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4511870.0</t>
+          <t>4989374.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>6073354.68</t>
+          <t>6088981.8</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>6426561</v>
+        <v>4880918</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2337,265 +2337,265 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
+          <t>60.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>60.5</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>60.18</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>61.05</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-110.23</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>13846853.24892396</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>6426561.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>4511870.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>3954850.9</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>6073354.68</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>557019</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-196415.2041115164</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>64065.21775619034</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>6426561</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>7336</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>60.98</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>60.17</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-111.80</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>13862341.85560345</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>4353182.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4057381.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>4284375.6</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>6008820.04</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-226994</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-243775.2808147359</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-117216.2015681742</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>4353182</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>22.18</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,57 +2758,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>60.98</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3692078.8</t>
+          <t>4057381.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>5967041.12</t>
+          <t>6008820.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6108693</v>
+        <v>4353182</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,42 +3063,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,280 +3194,280 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>13846853.24892396</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-149855.61483269</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>6108693</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>7336</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>13862341.85560345</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-379221.8261094019</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>3177516</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>22.18</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,104 +3499,104 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,32 +3645,32 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-379289.527000797</t>
+          <t>-379221.8261094019</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>2493398</v>
+        <v>3177516</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3935,89 +3935,89 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,280 +4066,280 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>13846853.24892396</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-379289.527000797</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>2493398</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>16.55</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>7336</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>13862341.85560345</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-292541.8308813325</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>4154116</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>6.17</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>22.18</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.488</t>
+          <t>68.327</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-25.16</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,42 +4517,42 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,50 +4592,50 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-336102.6996077644</t>
+          <t>-292541.8308813325</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2526671</v>
+        <v>4154116</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,42 +4807,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>41.488</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>46.504</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>93.16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.05999999999999</t>
+          <t>60.26000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.88</t>
+          <t>-118.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2843651.0</t>
+          <t>2526671.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5017353.6</t>
+          <t>4511370.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4610095.3</t>
+          <t>4642479.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>5974136.06</t>
+          <t>5957114.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>407258</t>
+          <t>-131109</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-227808.4429917456</t>
+          <t>-244469.0978557485</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-211959.7370881038</t>
+          <t>-336102.6996077644</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2843651</v>
+        <v>2526671</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>83.932</t>
+          <t>46.504</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-22 00:00:00</t>
+          <t>2025-11-25 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.70</t>
+          <t>10.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,64 +5389,64 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>60.05999999999999</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>60.51</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>60.76</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>60.13</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>-0.22</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>59.92</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>60.58</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>60.71</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-38.95</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.22</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>1.16</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.72</t>
+          <t>-118.88</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13862341.85560345</t>
+          <t>13846853.24892396</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5086341.0</t>
+          <t>2843651.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5219933.4</t>
+          <t>5017353.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4784238.5</t>
+          <t>4610095.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>5969370.9</t>
+          <t>5974136.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>435694</t>
+          <t>407258</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-230690.0258833168</t>
+          <t>-227808.4429917456</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-61004.80002115574</t>
+          <t>-211959.7370881038</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>5086341</v>
+        <v>2843651</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>16.55</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,42 +8005,42 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,17 +8862,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8882,59 +8882,59 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,57 +9298,57 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9561,17 +9561,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-5741199.813781753</t>
+          <t>-6375046.039764259</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>27154672</v>
+        <v>11143003</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,64 +10185,64 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6346198.319028817</t>
+          <t>-5741199.813781753</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>22755797</v>
+        <v>27154672</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.72</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>61.21</t>
+          <t>61.24</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>4182707.8</t>
+          <t>3567330.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>6008274.14</t>
+          <t>5919279.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>2044522</v>
+        <v>1276296</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.21</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4995542.0</t>
+          <t>4182707.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>6064700.48</t>
+          <t>6008274.14</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>3208356</v>
+        <v>2044522</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,27 +1891,27 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,50 +1976,50 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4989374.0</t>
+          <t>4995542.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>6088981.8</t>
+          <t>6064700.48</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>4880918</v>
+        <v>3208356</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,50 +2412,50 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4511870.0</t>
+          <t>4989374.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>6073354.68</t>
+          <t>6088981.8</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6426561</v>
+        <v>4880918</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2585,17 +2585,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2773,265 +2773,265 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>60.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>60.5</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>60.18</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>61.05</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-110.23</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>13829758.10673353</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>6426561.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>4511870.0</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>3954850.9</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>6073354.68</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>557019</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-196415.2041115164</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>64065.21775619034</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>6426561</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>24.99</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>7312</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>60.98</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>60.17</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-111.80</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>13846853.24892396</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>4353182.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4057381.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>4284375.6</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>6008820.04</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-226994</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-243775.2808147359</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-117216.2015681742</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>4353182</v>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>6.19</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>7336</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,52 +3199,52 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>60.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,50 +3284,50 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3692078.8</t>
+          <t>4057381.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>5967041.12</t>
+          <t>6008820.04</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>6108693</v>
+        <v>4353182</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,42 +3499,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,275 +3635,275 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>13829758.10673353</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-149855.61483269</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>6108693</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>24.99</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>7312</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>13846853.24892396</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-379221.8261094019</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>3177516</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>6.19</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>7336</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,104 +3935,104 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,32 +4081,32 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,50 +4156,50 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-379289.527000797</t>
+          <t>-379221.8261094019</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>2493398</v>
+        <v>3177516</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4371,89 +4371,89 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,275 +4507,275 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>13829758.10673353</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-379289.527000797</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>2493398</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>16.5</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>24.99</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>7312</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>13846853.24892396</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-292541.8308813325</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>4154116</v>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>6.19</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>16.55</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>7336</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41.488</t>
+          <t>68.327</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-25.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,42 +4953,42 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -4998,17 +4998,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-336102.6996077644</t>
+          <t>-292541.8308813325</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>2526671</v>
+        <v>4154116</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5243,42 +5243,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>41.488</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>46.504</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-25 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.92</t>
+          <t>9.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>93.16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.05999999999999</t>
+          <t>60.26000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.49</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>60.13</t>
+          <t>60.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>14.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.88</t>
+          <t>-118.23</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13846853.24892396</t>
+          <t>13829758.10673353</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2843651.0</t>
+          <t>2526671.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5017353.6</t>
+          <t>4511370.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4610095.3</t>
+          <t>4642479.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>5974136.06</t>
+          <t>5957114.36</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>407258</t>
+          <t>-131109</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-227808.4429917456</t>
+          <t>-244469.0978557485</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-211959.7370881038</t>
+          <t>-336102.6996077644</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2843651</v>
+        <v>2526671</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>274.793</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>307.156</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,42 +5810,42 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5855,32 +5855,32 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21316600.4</t>
+          <t>15743790.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>67714501.66</t>
+          <t>65312254.98</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>15825778</v>
+        <v>14210191</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,42 +8441,42 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8486,17 +8486,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,17 +9298,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9318,59 +9318,59 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,57 +9734,57 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9997,17 +9997,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-5741199.813781753</t>
+          <t>-6375046.039764259</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>27154672</v>
+        <v>11143003</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>76.46</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>61.67999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>60.72</t>
+          <t>60.79</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>61.24</t>
+          <t>61.23</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>616.57</t>
+          <t>276.58</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-98.32</t>
+          <t>-94.57</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,50 +1104,50 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>3567330.6</t>
+          <t>3230711.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3812355.8</t>
+          <t>3871290.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>5919279.24</t>
+          <t>5481764.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-245025</t>
+          <t>-640579</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-187334.6886499904</t>
+          <t>-195410.1823116441</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-389483.3332099607</t>
+          <t>-239825.39745074</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1276296</v>
+        <v>4743463</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>60.72</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>61.21</t>
+          <t>61.24</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,50 +1540,50 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>4182707.8</t>
+          <t>3567330.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>6008274.14</t>
+          <t>5919279.24</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2044522</v>
+        <v>1276296</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>60.62</t>
+          <t>60.67</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>61.21</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,50 +1976,50 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>4995542.0</t>
+          <t>4182707.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>6064700.48</t>
+          <t>6008274.14</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>3208356</v>
+        <v>2044522</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,27 +2327,27 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2357,42 +2357,42 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>60.56</t>
+          <t>60.62</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,50 +2412,50 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>4989374.0</t>
+          <t>4995542.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>6088981.8</t>
+          <t>6064700.48</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>4880918</v>
+        <v>3208356</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.56</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>61.03</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,50 +2848,50 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>4511870.0</t>
+          <t>4989374.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>6073354.68</t>
+          <t>6088981.8</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6426561</v>
+        <v>4880918</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,265 +3209,265 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>60.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>60.5</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>61.03</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>60.18</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>61.05</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-110.23</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>13820152.15021459</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>6426561.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>4511870.0</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>3954850.9</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>6073354.68</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>557019</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-196415.2041115164</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>64065.21775619034</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>6426561</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>7455</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>61.7</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>60.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>60.98</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>60.17</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>45.24</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.07</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-111.80</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>13829758.10673353</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>4353182.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4057381.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>4284375.6</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6008820.04</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-226994</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-243775.2808147359</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-117216.2015681742</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>4353182</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>24.99</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>7312</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>61.2</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,52 +3635,52 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>60.51</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>60.98</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,50 +3720,50 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3692078.8</t>
+          <t>4057381.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>5967041.12</t>
+          <t>6008820.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>6108693</v>
+        <v>4353182</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,42 +3935,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,275 +4071,275 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>60.51</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>60.95</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-113.13</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>13820152.15021459</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>3692078.8</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>4354716.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>5967041.12</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-662637</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-266786.0224959289</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-149855.61483269</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>6108693</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-0.65</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>7455</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>32.21</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-114.69</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>13829758.10673353</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>3177516.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>4129501.9</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-1090431</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-288046.0966165178</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-379221.8261094019</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>3177516</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-1.14</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>24.99</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>7312</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,104 +4371,104 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,32 +4517,32 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60.86</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,50 +4592,50 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3420835.4</t>
+          <t>3039070.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>5950257.14</t>
+          <t>5900269.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-379289.527000797</t>
+          <t>-379221.8261094019</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>2493398</v>
+        <v>3177516</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4807,89 +4807,89 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,275 +4943,275 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>60.46</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>60.86</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>13820152.15021459</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>3420835.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>5950257.14</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-379289.527000797</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>2493398</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>7455</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>13829758.10673353</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-292541.8308813325</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>4154116</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>24.99</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>7312</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41.488</t>
+          <t>68.327</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-25.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-26 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.8</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>16.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,42 +5389,42 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.26000000000001</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>60.49</t>
+          <t>60.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>60.83</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -5434,17 +5434,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>14.22</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-118.23</t>
+          <t>-117.07</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,50 +5464,50 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13829758.10673353</t>
+          <t>13820152.15021459</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2526671.0</t>
+          <t>4154116.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>4511370.2</t>
+          <t>3397831.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4642479.4</t>
+          <t>4539831.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>5957114.36</t>
+          <t>5993919.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-131109</t>
+          <t>-1141999</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-244469.0978557485</t>
+          <t>-251864.9029366076</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-336102.6996077644</t>
+          <t>-292541.8308813325</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2526671</v>
+        <v>4154116</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7312</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,72 +5815,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>55.01</t>
+          <t>54.78</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>15743790.2</t>
+          <t>14968564.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>65312254.98</t>
+          <t>55328963.9</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>14210191</v>
+        <v>16370637</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,37 +6251,37 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -6291,32 +6291,32 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21316600.4</t>
+          <t>15743790.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>67714501.66</t>
+          <t>65312254.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>15825778</v>
+        <v>14210191</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,17 +6940,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,127 +7423,127 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>217.689</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>-0.38</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>392.184</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-14.63</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>0.39</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-4.66</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>28.13</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-15.93</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>0.21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,42 +8877,42 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9754,59 +9754,59 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,52 +10175,52 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10433,17 +10433,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>61.67999999999999</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>60.79</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>61.23</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>60.79</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>61.23</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>4743463.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3230711.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>3230711</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>3871290.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>5481764.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>5481764.24</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-239825.39745074</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>4743463</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4743463.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>61.38</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>60.72</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>61.24</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>60.72</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>61.24</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1276296.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>3567330.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>3567330.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>3812355.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>5919279.24</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>5919279.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-389483.3332099607</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1276296</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1276296.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>61.26000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>60.67</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>61.21</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>61.21</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2044522.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4182707.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>4182707.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>3937393.3</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>6008274.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>6008274.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-217888.0866799201</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2044522</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2044522.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>61.15999999999999</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>60.62</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>61.16</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>61.16</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>3208356.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4995542.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4995542</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>4017306.2</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>6064700.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>6064700.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-47280.23139843624</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>3208356</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>3208356.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.96</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>60.56</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>61.1</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>61.1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>4880918.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989374.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989374</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>4205104.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>6088981.8</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>6088981.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>73437.35583934188</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>4880918</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>4880918.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>60.72000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>61.03</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6426561.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4511870.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>4511870</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>3954850.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>6073354.68</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>6073354.68</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>64065.21775619034</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6426561</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6426561.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>60.7</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>60.98</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>60.98</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>4353182.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4057381.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>4057381</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>4284375.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>6008820.04</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>6008820.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-117216.2015681742</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>4353182</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>4353182.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>60.73999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>60.51</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>60.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>60.51</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>60.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>6108693.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3692078.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>3692078.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>4354716.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>5967041.12</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>5967041.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-149855.61483269</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>6108693</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>6108693.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>60.76000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>60.46</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>60.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>3177516.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3039070.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3039070.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>4129501.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>5900269.22</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>5900269.22</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-379221.8261094019</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>3177516</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>3177516.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>60.84</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>60.46</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>60.86</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60.86</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2493398.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3420835.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>3420835.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>4358274.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>5950257.14</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>5950257.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-379289.527000797</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2493398</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>60.6</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>60.48</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>60.83</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>4154116.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3397831.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>3397831.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>4539831.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>5993919.22</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>5993919.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-292541.8308813325</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>4154116</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>4154116.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>54.78</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>58.02</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>16370637.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>14968564.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>14968564.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>25991927.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>55328963.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>55328963.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3761738.343921479</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>16370637</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>16370637.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>14210191.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>15743790.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>15743790.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>25956465.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>65312254.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>65312254.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3880161.860334959</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>14210191</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>14210191.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>55.27</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>15825778.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>21316600.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>21316600.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>25649746.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>67714501.66</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>67714501.66</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3679284.745913677</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>15825778</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>15825778.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>52.14</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>17027345.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>22754558.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>22754558</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>26782636.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>69191727.6</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>69191727.59999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-3434013.020100649</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>17027345</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>17027345.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>58.83</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>11408872.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>28718377.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>28718377.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>27355481.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>69373581.34</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>69373581.34</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3089720.839649871</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>11408872</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>11408872.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>58.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>20246765.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>37015290.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>37015290.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>28888889.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>69945836.02</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>69945836.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1885548.444732688</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>20246765</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>20246765.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>54.21999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>59.12</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>42074242.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>36169141.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>36169141.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>29060387.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>70323701.58</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>70323701.58</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1044878.257539123</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>42074242</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>42074242.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>55.12</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>23015566.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>29982893.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>29982893.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>27325142.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>70871687.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>70871687.59999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-2145262.016636197</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>23015566</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>57.07</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>59.42</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>46846442.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>30810714.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>30810714.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>28427276.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>71965384.46</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>71965384.45999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-1598621.314752154</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>46846442</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>52893437.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>25992585.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>25992585.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>25254632.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>72823093.42</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>72823093.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3313920.550819516</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>52893437</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>16016019.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>20762488.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>20762488.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>23044675.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>73396602.94</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>73396602.94</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-6293886.04695791</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>16016019</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>144.632</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,87 +898,87 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-10.04</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>62.4</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-16.55</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>61.67999999999999</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>60.79</v>
+        <v>60.91</v>
       </c>
       <c r="AN2" t="n">
-        <v>61.23</v>
+        <v>61.27</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>60.43</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>276.58</t>
+          <t>204.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.57</t>
+          <t>-88.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3230711</v>
+        <v>4079143.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3871290.5</t>
+          <t>4534258.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>5481764.24</v>
+        <v>5466906.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-640579</t>
+          <t>-455115</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-195410.1823116441</t>
+          <t>-134669.8361841631</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-239825.39745074</t>
+          <t>199402.0675169826</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>76.46</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>61.67999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>60.72</v>
+        <v>60.79</v>
       </c>
       <c r="AN3" t="n">
-        <v>61.24</v>
+        <v>61.23</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>616.57</t>
+          <t>276.58</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-98.32</t>
+          <t>-94.57</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3567330.6</v>
+        <v>3230711</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3812355.8</t>
+          <t>3871290.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>5919279.24</v>
+        <v>5481764.24</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-245025</t>
+          <t>-640579</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-187334.6886499904</t>
+          <t>-195410.1823116441</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-389483.3332099607</t>
+          <t>-239825.39745074</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>60.67</v>
+        <v>60.72</v>
       </c>
       <c r="AN4" t="n">
-        <v>61.21</v>
+        <v>61.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4182707.8</v>
+        <v>3567330.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>6008274.14</v>
+        <v>5919279.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>60.62</v>
+        <v>60.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>61.16</v>
+        <v>61.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4995542</v>
+        <v>4182707.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>6064700.48</v>
+        <v>6008274.14</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,32 +2734,32 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2769,38 +2769,38 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>60.56</v>
+        <v>60.62</v>
       </c>
       <c r="AN6" t="n">
-        <v>61.1</v>
+        <v>61.16</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4989374</v>
+        <v>4995542</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>6088981.8</v>
+        <v>6064700.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>60.5</v>
+        <v>60.56</v>
       </c>
       <c r="AN7" t="n">
-        <v>61.03</v>
+        <v>61.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4511870</v>
+        <v>4989374</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>6073354.68</v>
+        <v>6088981.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>60.72000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
         <v>60.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>60.98</v>
+        <v>61.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.18</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>61.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4057381</v>
+        <v>4511870</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4284375.6</t>
+          <t>3954850.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>6008820.04</v>
+        <v>6073354.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-226994</t>
+          <t>557019</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-243775.2808147359</t>
+          <t>-196415.2041115164</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-117216.2015681742</t>
+          <t>64065.21775619034</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>60.51</v>
+        <v>60.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.95</v>
+        <v>60.98</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3692078.8</v>
+        <v>4057381</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>5967041.12</v>
+        <v>6008820.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,42 +4323,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>60.46</v>
+        <v>60.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.9</v>
+        <v>60.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-113.13</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3177516.0</t>
+          <t>6108693.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3039070.4</v>
+        <v>3692078.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4129501.9</t>
+          <t>4354716.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>5900269.22</v>
+        <v>5967041.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1090431</t>
+          <t>-662637</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-288046.0966165178</t>
+          <t>-266786.0224959289</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-379221.8261094019</t>
+          <t>-149855.61483269</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3177516.0</t>
+          <t>6108693.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,104 +4753,104 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>60.46</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.86</v>
+        <v>60.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13820152.15021459</t>
+          <t>13819958.53285714</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3420835.4</v>
+        <v>3039070.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>5950257.14</v>
+        <v>5900269.22</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-379289.527000797</t>
+          <t>-379221.8261094019</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7574</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,17 +5136,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5183,89 +5183,89 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>41.147</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.42</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>68.327</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-21.51</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-25.16</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>60.8</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>62.8</t>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.04</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,274 +5314,274 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>145</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>78.95</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>60.84</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>30.05</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-115.88</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/11</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>13819958.53285714</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>3420835.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>4358274.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>5950257.14</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-937439</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-271468.6912541752</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-379289.527000797</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2493398.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>61.3</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/16</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>6.623031455188929</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>3.641068997764138</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-2.243137714835828</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>5.99</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>10.06</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>17.09</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>58.62%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>7574</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>宏正-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>60.6</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>60.14</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-117.07</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>13820152.15021459</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>3397831.8</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>4539831.7</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>5993919.22</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-1141999</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-251864.9029366076</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-292541.8308813325</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>4154116.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>61.3</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/09/16</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>宏正</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>6.623031455188929</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>3.641068997764138</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-2.243137714835828</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>58.62%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>11.94%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>26.25</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>7455</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>IT架構管理解決方案63.10%、其他20.39%、視訊產品16.51% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>宏正-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>60.7</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>60.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN14" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,42 +6604,42 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -6648,29 +6648,29 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN19" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,39 +9199,39 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN21" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.31</v>
+        <v>57.07</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.56</v>
+        <v>59.42</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>25992585.6</v>
+        <v>30810714.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>72823093.42</v>
+        <v>71965384.45999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,17 +10044,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10064,55 +10064,55 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.52</v>
+        <v>57.31</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.68</v>
+        <v>59.56</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>20762488.6</v>
+        <v>25992585.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>73396602.94</v>
+        <v>72823093.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>144.632</t>
+          <t>167.119</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>60.91</v>
+        <v>61.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>61.27</v>
+        <v>61.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.43</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>204.14</t>
+          <t>164.83</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.91</t>
+          <t>-81.14</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4079143.4</v>
+        <v>5580574.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4534258.7</t>
+          <t>5288058.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>5466906.8</v>
+        <v>5581986.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-455115</t>
+          <t>292516</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-134669.8361841631</t>
+          <t>-18365.44349329743</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>199402.0675169826</t>
+          <t>621308.7163064638</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>144.632</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,87 +1328,87 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-10.04</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>62.4</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-16.55</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>61.67999999999999</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>60.79</v>
+        <v>60.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>61.23</v>
+        <v>61.27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>60.43</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>276.58</t>
+          <t>204.14</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-94.57</t>
+          <t>-88.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3230711</v>
+        <v>4079143.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3871290.5</t>
+          <t>4534258.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>5481764.24</v>
+        <v>5466906.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-640579</t>
+          <t>-455115</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-195410.1823116441</t>
+          <t>-134669.8361841631</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-239825.39745074</t>
+          <t>199402.0675169826</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>76.46</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>61.67999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>60.72</v>
+        <v>60.79</v>
       </c>
       <c r="AN4" t="n">
-        <v>61.24</v>
+        <v>61.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>616.57</t>
+          <t>276.58</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-98.32</t>
+          <t>-94.57</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3567330.6</v>
+        <v>3230711</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3812355.8</t>
+          <t>3871290.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>5919279.24</v>
+        <v>5481764.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-245025</t>
+          <t>-640579</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-187334.6886499904</t>
+          <t>-195410.1823116441</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-389483.3332099607</t>
+          <t>-239825.39745074</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>60.67</v>
+        <v>60.72</v>
       </c>
       <c r="AN5" t="n">
-        <v>61.21</v>
+        <v>61.24</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4182707.8</v>
+        <v>3567330.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>6008274.14</v>
+        <v>5919279.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>60.62</v>
+        <v>60.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>61.16</v>
+        <v>61.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4995542</v>
+        <v>4182707.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>6064700.48</v>
+        <v>6008274.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,32 +3164,32 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3199,38 +3199,38 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>60.56</v>
+        <v>60.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>61.1</v>
+        <v>61.16</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4989374</v>
+        <v>4995542</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>6088981.8</v>
+        <v>6064700.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>60.5</v>
+        <v>60.56</v>
       </c>
       <c r="AN8" t="n">
-        <v>61.03</v>
+        <v>61.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4511870</v>
+        <v>4989374</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>6073354.68</v>
+        <v>6088981.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>60.72000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
         <v>60.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>60.98</v>
+        <v>61.03</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.18</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>61.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4057381</v>
+        <v>4511870</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4284375.6</t>
+          <t>3954850.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>6008820.04</v>
+        <v>6073354.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-226994</t>
+          <t>557019</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-243775.2808147359</t>
+          <t>-196415.2041115164</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-117216.2015681742</t>
+          <t>64065.21775619034</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>60.51</v>
+        <v>60.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.95</v>
+        <v>60.98</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3692078.8</v>
+        <v>4057381</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>5967041.12</v>
+        <v>6008820.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,42 +4753,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>60.46</v>
+        <v>60.51</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.9</v>
+        <v>60.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-113.13</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3177516.0</t>
+          <t>6108693.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3039070.4</v>
+        <v>3692078.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4129501.9</t>
+          <t>4354716.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>5900269.22</v>
+        <v>5967041.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1090431</t>
+          <t>-662637</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-288046.0966165178</t>
+          <t>-266786.0224959289</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-379221.8261094019</t>
+          <t>-149855.61483269</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3177516.0</t>
+          <t>6108693.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,104 +5183,104 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>52.567</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-26.41</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>62.4</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>41.147</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4.42</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-21.51</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.84</t>
+          <t>60.76000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>60.46</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.86</v>
+        <v>60.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>32.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-115.88</t>
+          <t>-114.69</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13819958.53285714</t>
+          <t>13823172.95649073</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3420835.4</v>
+        <v>3039070.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4358274.7</t>
+          <t>4129501.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>5950257.14</v>
+        <v>5900269.22</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-937439</t>
+          <t>-1090431</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-271468.6912541752</t>
+          <t>-288046.0966165178</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-379289.527000797</t>
+          <t>-379221.8261094019</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2493398.0</t>
+          <t>3177516.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7574</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>60.9</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>60.9</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN14" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,42 +7034,42 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -7078,29 +7078,29 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN20" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN21" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,39 +9629,39 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.31</v>
+        <v>57.07</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.56</v>
+        <v>59.42</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>25992585.6</v>
+        <v>30810714.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>72823093.42</v>
+        <v>71965384.45999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>167.119</t>
+          <t>117.566</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>62.95999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>61.1</v>
+        <v>61.26</v>
       </c>
       <c r="AN2" t="n">
-        <v>61.35</v>
+        <v>61.39</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>164.83</t>
+          <t>114.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>-73.59</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10715513.0</t>
+          <t>7504121.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5580574.8</v>
+        <v>6672494.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5288058.4</t>
+          <t>5427601.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>5581986.58</v>
+        <v>5462127.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>292516</t>
+          <t>1244893</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-18365.44349329743</t>
+          <t>86037.89435973913</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>621308.7163064638</t>
+          <t>660256.2525514401</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10715513.0</t>
+          <t>7504121.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>63.5</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>64.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>144.632</t>
+          <t>167.119</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>60.91</v>
+        <v>61.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>61.27</v>
+        <v>61.35</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.43</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>204.14</t>
+          <t>164.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.91</t>
+          <t>-81.14</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4079143.4</v>
+        <v>5580574.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4534258.7</t>
+          <t>5288058.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>5466906.8</v>
+        <v>5581986.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-455115</t>
+          <t>292516</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-134669.8361841631</t>
+          <t>-18365.44349329743</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>199402.0675169826</t>
+          <t>621308.7163064638</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>144.632</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,87 +1758,87 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-10.04</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>62.4</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-16.55</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>61.67999999999999</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>60.79</v>
+        <v>60.91</v>
       </c>
       <c r="AN4" t="n">
-        <v>61.23</v>
+        <v>61.27</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>60.43</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>276.58</t>
+          <t>204.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.57</t>
+          <t>-88.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3230711</v>
+        <v>4079143.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3871290.5</t>
+          <t>4534258.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>5481764.24</v>
+        <v>5466906.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-640579</t>
+          <t>-455115</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-195410.1823116441</t>
+          <t>-134669.8361841631</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-239825.39745074</t>
+          <t>199402.0675169826</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>76.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>61.67999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>60.72</v>
+        <v>60.79</v>
       </c>
       <c r="AN5" t="n">
-        <v>61.24</v>
+        <v>61.23</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>616.57</t>
+          <t>276.58</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-98.32</t>
+          <t>-94.57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3567330.6</v>
+        <v>3230711</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3812355.8</t>
+          <t>3871290.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>5919279.24</v>
+        <v>5481764.24</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-245025</t>
+          <t>-640579</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-187334.6886499904</t>
+          <t>-195410.1823116441</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-389483.3332099607</t>
+          <t>-239825.39745074</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>60.67</v>
+        <v>60.72</v>
       </c>
       <c r="AN6" t="n">
-        <v>61.21</v>
+        <v>61.24</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>4182707.8</v>
+        <v>3567330.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>6008274.14</v>
+        <v>5919279.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>60.62</v>
+        <v>60.67</v>
       </c>
       <c r="AN7" t="n">
-        <v>61.16</v>
+        <v>61.21</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4995542</v>
+        <v>4182707.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>6064700.48</v>
+        <v>6008274.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,32 +3594,32 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3629,38 +3629,38 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>60.56</v>
+        <v>60.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>61.1</v>
+        <v>61.16</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4989374</v>
+        <v>4995542</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>6088981.8</v>
+        <v>6064700.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>60.5</v>
+        <v>60.56</v>
       </c>
       <c r="AN9" t="n">
-        <v>61.03</v>
+        <v>61.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4511870</v>
+        <v>4989374</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>6073354.68</v>
+        <v>6088981.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>60.72000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
         <v>60.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>60.98</v>
+        <v>61.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.18</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>61.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4057381</v>
+        <v>4511870</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4284375.6</t>
+          <t>3954850.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>6008820.04</v>
+        <v>6073354.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-226994</t>
+          <t>557019</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-243775.2808147359</t>
+          <t>-196415.2041115164</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-117216.2015681742</t>
+          <t>64065.21775619034</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>60.51</v>
+        <v>60.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.95</v>
+        <v>60.98</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4970,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3692078.8</v>
+        <v>4057381</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>5967041.12</v>
+        <v>6008820.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,42 +5183,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100.724</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>52.567</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>60.6</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.41</t>
+          <t>-15.22</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>23.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>94.74</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.76000000000001</t>
+          <t>60.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>60.46</v>
+        <v>60.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.9</v>
+        <v>60.95</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.17</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>47.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.69</t>
+          <t>-113.13</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,48 +5400,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13823172.95649073</t>
+          <t>13819516.27350427</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3177516.0</t>
+          <t>6108693.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3039070.4</v>
+        <v>3692078.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4129501.9</t>
+          <t>4354716.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>5900269.22</v>
+        <v>5967041.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1090431</t>
+          <t>-662637</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-288046.0966165178</t>
+          <t>-266786.0224959289</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-379221.8261094019</t>
+          <t>-149855.61483269</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3177516.0</t>
+          <t>6108693.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>60.4</t>
+          <t>60.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>60.9</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>60.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>60.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,102 +6068,102 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-23.55</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-14.63</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>0.57</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-31.01</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-15.12</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-1.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,42 +7464,42 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -7508,29 +7508,29 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN20" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN21" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,39 +10059,39 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>117.566</t>
+          <t>105.758</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,38 +993,38 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>62.95999999999999</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>61.26</v>
+        <v>61.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>61.39</v>
+        <v>61.46</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>114.27</t>
+          <t>93.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-73.59</t>
+          <t>-65.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,63 +1100,63 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7504121.0</t>
+          <t>6835379.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>6672494.6</v>
+        <v>7784311.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5427601.2</t>
+          <t>5675820.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>5462127.84</v>
+        <v>5504596.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>1244893</t>
+          <t>2108490</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>86037.89435973913</t>
+          <t>168317.8293211848</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>660256.2525514401</t>
+          <t>620857.4716091361</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7504121.0</t>
+          <t>6835379.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>64.3</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>63.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>167.119</t>
+          <t>117.566</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>62.95999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>61.1</v>
+        <v>61.26</v>
       </c>
       <c r="AN3" t="n">
-        <v>61.35</v>
+        <v>61.39</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>164.83</t>
+          <t>114.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>-73.59</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,63 +1530,63 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10715513.0</t>
+          <t>7504121.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5580574.8</v>
+        <v>6672494.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5288058.4</t>
+          <t>5427601.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>5581986.58</v>
+        <v>5462127.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>292516</t>
+          <t>1244893</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-18365.44349329743</t>
+          <t>86037.89435973913</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>621308.7163064638</t>
+          <t>660256.2525514401</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>10715513.0</t>
+          <t>7504121.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>63.5</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>64.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>144.632</t>
+          <t>167.119</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>60.91</v>
+        <v>61.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>61.27</v>
+        <v>61.35</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.43</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>204.14</t>
+          <t>164.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.91</t>
+          <t>-81.14</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,63 +1960,63 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>4079143.4</v>
+        <v>5580574.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4534258.7</t>
+          <t>5288058.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>5466906.8</v>
+        <v>5581986.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-455115</t>
+          <t>292516</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-134669.8361841631</t>
+          <t>-18365.44349329743</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>199402.0675169826</t>
+          <t>621308.7163064638</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>144.632</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,87 +2188,87 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-10.04</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>62.4</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-16.55</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>61.67999999999999</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>60.79</v>
+        <v>60.91</v>
       </c>
       <c r="AN5" t="n">
-        <v>61.23</v>
+        <v>61.27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>60.43</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>276.58</t>
+          <t>204.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-94.57</t>
+          <t>-88.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,63 +2390,63 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3230711</v>
+        <v>4079143.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3871290.5</t>
+          <t>4534258.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>5481764.24</v>
+        <v>5466906.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-640579</t>
+          <t>-455115</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-195410.1823116441</t>
+          <t>-134669.8361841631</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-239825.39745074</t>
+          <t>199402.0675169826</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>76.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>61.67999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>60.72</v>
+        <v>60.79</v>
       </c>
       <c r="AN6" t="n">
-        <v>61.24</v>
+        <v>61.23</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>616.57</t>
+          <t>276.58</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-98.32</t>
+          <t>-94.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,63 +2820,63 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3567330.6</v>
+        <v>3230711</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3812355.8</t>
+          <t>3871290.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>5919279.24</v>
+        <v>5481764.24</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-245025</t>
+          <t>-640579</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-187334.6886499904</t>
+          <t>-195410.1823116441</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-389483.3332099607</t>
+          <t>-239825.39745074</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>60.67</v>
+        <v>60.72</v>
       </c>
       <c r="AN7" t="n">
-        <v>61.21</v>
+        <v>61.24</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,63 +3250,63 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>4182707.8</v>
+        <v>3567330.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>6008274.14</v>
+        <v>5919279.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>60.62</v>
+        <v>60.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>61.16</v>
+        <v>61.21</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,63 +3680,63 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4995542</v>
+        <v>4182707.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>6064700.48</v>
+        <v>6008274.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,32 +4024,32 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4059,38 +4059,38 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>60.56</v>
+        <v>60.62</v>
       </c>
       <c r="AN9" t="n">
-        <v>61.1</v>
+        <v>61.16</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,63 +4110,63 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4989374</v>
+        <v>4995542</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>6088981.8</v>
+        <v>6064700.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>784269</t>
+          <t>978235</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-154899.4256575382</t>
+          <t>-138342.6265407533</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>73437.35583934188</t>
+          <t>-47280.23139843624</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>61.8</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>61.0</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>105.229</t>
+          <t>79.207</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14.08</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.70</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>81.58</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.72000000000001</t>
+          <t>60.96</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>60.5</v>
+        <v>60.56</v>
       </c>
       <c r="AN10" t="n">
-        <v>61.03</v>
+        <v>61.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.18</t>
+          <t>60.21</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>61.05</t>
+          <t>157.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.23</t>
+          <t>-107.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,63 +4540,63 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4511870</v>
+        <v>4989374</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3954850.9</t>
+          <t>4205104.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>6073354.68</v>
+        <v>6088981.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>557019</t>
+          <t>784269</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-196415.2041115164</t>
+          <t>-154899.4256575382</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>64065.21775619034</t>
+          <t>73437.35583934188</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6426561.0</t>
+          <t>4880918.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4711,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>61.7</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>61.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>71.959</t>
+          <t>105.229</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>14.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>24.70</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>81.58</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>60.72000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
         <v>60.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>60.98</v>
+        <v>61.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.18</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>61.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.80</t>
+          <t>-110.23</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,63 +4970,63 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>4057381</v>
+        <v>4511870</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4284375.6</t>
+          <t>3954850.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>6008820.04</v>
+        <v>6073354.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-226994</t>
+          <t>557019</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-243775.2808147359</t>
+          <t>-196415.2041115164</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-117216.2015681742</t>
+          <t>64065.21775619034</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4353182.0</t>
+          <t>6426561.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>100.724</t>
+          <t>71.959</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-5.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23.64</t>
+          <t>16.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>94.74</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>60.73999999999999</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>60.51</v>
+        <v>60.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>60.95</v>
+        <v>60.98</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-113.13</t>
+          <t>-111.80</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,63 +5400,63 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>13819516.27350427</t>
+          <t>13814443.09032717</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3692078.8</v>
+        <v>4057381</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4354716.2</t>
+          <t>4284375.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>5967041.12</v>
+        <v>6008820.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-662637</t>
+          <t>-226994</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-266786.0224959289</t>
+          <t>-243775.2808147359</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-149855.61483269</t>
+          <t>-117216.2015681742</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6108693.0</t>
+          <t>4353182.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/09/16</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.98</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>17.33</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,68 +6604,68 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,42 +7894,42 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -7938,29 +7938,29 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,17 +8576,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN20" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN21" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控管理.xlsx
+++ b/Result/checksun_type/監控管理.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>105.758</t>
+          <t>53.08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>93.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>92.16</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>63.91999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>61.48</v>
+        <v>61.73</v>
       </c>
       <c r="AN2" t="n">
-        <v>61.46</v>
+        <v>61.52</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>93.43</t>
+          <t>72.19</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-65.54</t>
+          <t>-57.96</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6835379.0</t>
+          <t>3394480.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7784311.2</v>
+        <v>7514514.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5675820.9</t>
+          <t>5372612.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>5504596.92</v>
+        <v>5482173.54</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2108490</t>
+          <t>2141901</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>168317.8293211848</t>
+          <t>191605.7729885867</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>620857.4716091361</t>
+          <t>319689.4631592967</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6835379.0</t>
+          <t>3394480.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>117.566</t>
+          <t>105.758</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>22.94</t>
+          <t>37.15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,38 +1423,38 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>62.95999999999999</t>
+          <t>63.58</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>61.26</v>
+        <v>61.48</v>
       </c>
       <c r="AN3" t="n">
-        <v>61.39</v>
+        <v>61.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>60.6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>114.27</t>
+          <t>93.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-73.59</t>
+          <t>-65.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7504121.0</t>
+          <t>6835379.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>6672494.6</v>
+        <v>7784311.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5427601.2</t>
+          <t>5675820.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>5462127.84</v>
+        <v>5504596.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1244893</t>
+          <t>2108490</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>86037.89435973913</t>
+          <t>168317.8293211848</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>660256.2525514401</t>
+          <t>620857.4716091361</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7504121.0</t>
+          <t>6835379.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>64.3</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>63.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>167.119</t>
+          <t>117.566</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>22.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>39.23</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.16</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>62.54</t>
+          <t>62.95999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>61.1</v>
+        <v>61.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>61.35</v>
+        <v>61.39</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>164.83</t>
+          <t>114.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-81.14</t>
+          <t>-73.59</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10715513.0</t>
+          <t>7504121.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5580574.8</v>
+        <v>6672494.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5288058.4</t>
+          <t>5427601.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>5581986.58</v>
+        <v>5462127.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>292516</t>
+          <t>1244893</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-18365.44349329743</t>
+          <t>86037.89435973913</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>621308.7163064638</t>
+          <t>660256.2525514401</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10715513.0</t>
+          <t>7504121.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>63.5</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>64.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>144.632</t>
+          <t>167.119</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.04</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>39.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>62.54</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>60.91</v>
+        <v>61.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>61.27</v>
+        <v>61.35</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>60.43</t>
+          <t>60.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>204.14</t>
+          <t>164.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.91</t>
+          <t>-81.14</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>4079143.4</v>
+        <v>5580574.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4534258.7</t>
+          <t>5288058.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>5466906.8</v>
+        <v>5581986.58</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-455115</t>
+          <t>292516</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-134669.8361841631</t>
+          <t>-18365.44349329743</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>199402.0675169826</t>
+          <t>621308.7163064638</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9123080.0</t>
+          <t>10715513.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>63.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>63.4</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>76.46</t>
+          <t>144.632</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,87 +2618,87 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-10.04</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>60.8</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>62.8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>62.4</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-16.55</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>60.8</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>62.8</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>62.4</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.22</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>61.67999999999999</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>60.79</v>
+        <v>60.91</v>
       </c>
       <c r="AN6" t="n">
-        <v>61.23</v>
+        <v>61.27</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>60.43</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>276.58</t>
+          <t>204.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-94.57</t>
+          <t>-88.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3230711</v>
+        <v>4079143.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3871290.5</t>
+          <t>4534258.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>5481764.24</v>
+        <v>5466906.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-640579</t>
+          <t>-455115</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-195410.1823116441</t>
+          <t>-134669.8361841631</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-239825.39745074</t>
+          <t>199402.0675169826</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4743463.0</t>
+          <t>9123080.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>76.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>72.22</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>61.38</t>
+          <t>61.67999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>60.72</v>
+        <v>60.79</v>
       </c>
       <c r="AN7" t="n">
-        <v>61.24</v>
+        <v>61.23</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>60.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>616.57</t>
+          <t>276.58</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-98.32</t>
+          <t>-94.57</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3567330.6</v>
+        <v>3230711</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3812355.8</t>
+          <t>3871290.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>5919279.24</v>
+        <v>5481764.24</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-245025</t>
+          <t>-640579</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-187334.6886499904</t>
+          <t>-195410.1823116441</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-389483.3332099607</t>
+          <t>-239825.39745074</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1276296.0</t>
+          <t>4743463.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-4.82</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>61.1</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>62.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>20.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.78</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>61.26000000000001</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>60.67</v>
+        <v>60.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>61.21</v>
+        <v>61.24</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>60.29</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1380.72</t>
+          <t>616.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.91</t>
+          <t>-98.32</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>4182707.8</v>
+        <v>3567330.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3937393.3</t>
+          <t>3812355.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>6008274.14</v>
+        <v>5919279.24</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>245314</t>
+          <t>-245025</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-150580.3896390867</t>
+          <t>-187334.6886499904</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-217888.0866799201</t>
+          <t>-389483.3332099607</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2044522.0</t>
+          <t>1276296.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.326</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>7.78</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>66.67</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>83.33</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>86.11</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>61.15999999999999</t>
+          <t>61.26000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>60.62</v>
+        <v>60.67</v>
       </c>
       <c r="AN9" t="n">
-        <v>61.16</v>
+        <v>61.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>60.25</t>
+          <t>60.29</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>327.64</t>
+          <t>1380.72</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.04</t>
+          <t>-100.91</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4110,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>4995542</v>
+        <v>4182707.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4017306.2</t>
+          <t>3937393.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>6064700.48</v>
+        <v>6008274.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>978235</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-138342.6265407533</t>
+          <t>-150580.3896390867</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-47280.23139843624</t>
+          <t>-217888.0866799201</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3208356.0</t>
+          <t>2044522.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>17.33</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>61.0</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>79.207</t>
+          <t>52.326</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>12.28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,32 +4454,32 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4489,38 +4489,38 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>61.15999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>60.56</v>
+        <v>60.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>61.1</v>
+        <v>61.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>60.21</t>
+          <t>60.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>157.22</t>
+          <t>327.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-107.35</t>
+          <t>-104.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>13814443.09032717</t>
+          <t>13802052.85866477</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4880918.0</t>
+          <t>3208356.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>4989374</v>
+        <v>4995542</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4205104.7</t>
+          <t>4017306.2</t>
        